--- a/excel/distribuidora-aurelio-s-a-c_ccc.xlsx
+++ b/excel/distribuidora-aurelio-s-a-c_ccc.xlsx
@@ -609,7 +609,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>19842</v>
+        <v>81356</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -643,12 +643,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>C001086594</t>
+          <t>C004178904</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C001086594 - RAMOS CAHUANA SONIA ISABEL</t>
+          <t>C004178904 - BELLEZA QUISPE ROSARIO PATRICIA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>S17840713</t>
+          <t>S17856822</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -708,12 +708,12 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -725,7 +725,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>27908</v>
+        <v>74548</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -759,12 +759,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>C001160082</t>
+          <t>C004180920</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>C001160082 - TORRES SIERRA SARA DEL ROSARIO</t>
+          <t>C004180920 - ORIHUELA VALENTIN EDELMIRA VICENTA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>S17845326</t>
+          <t>S17839069</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,7 +841,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4780</v>
+        <v>100614</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -875,12 +875,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>C000957808</t>
+          <t>C004065232</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>C000957808 - NAPANGA PEREZ BALBINA ISIDORA</t>
+          <t>C004065232 - AGUADO LOPEZ CHAI TIODOLINDA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>S17842189</t>
+          <t>S17842164</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -940,7 +940,7 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -950,14 +950,14 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>57661</v>
+        <v>97978</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -991,12 +991,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>C004016284</t>
+          <t>C001158905</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>C004016284 - QUINCHO QUINCHO MELCHORA FELICIA</t>
+          <t>C001158905 - DIAZ PEREZ ELIZABETH</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>S17849074</t>
+          <t>S17851802</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>No cuenta con presupuesto disponible en ese momento.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1056,7 +1056,7 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1073,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>54653</v>
+        <v>57661</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>C004037620</t>
+          <t>C004016284</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C004037620 - CAHUAPAS TORNERO MARILU NOELIA</t>
+          <t>C004016284 - QUINCHO QUINCHO MELCHORA FELICIA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>S17848829</t>
+          <t>S17849074</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No cuenta con presupuesto disponible en ese momento.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1189,7 +1189,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>81356</v>
+        <v>54653</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>C004178904</t>
+          <t>C004037620</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>C004178904 - BELLEZA QUISPE ROSARIO PATRICIA</t>
+          <t>C004037620 - CAHUAPAS TORNERO MARILU NOELIA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>S17856822</t>
+          <t>S17848829</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1305,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74548</v>
+        <v>27908</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>C004180920</t>
+          <t>C001160082</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C004180920 - ORIHUELA VALENTIN EDELMIRA VICENTA</t>
+          <t>C001160082 - TORRES SIERRA SARA DEL ROSARIO</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>S17839069</t>
+          <t>S17845326</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1421,7 +1421,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>100614</v>
+        <v>19842</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1455,12 +1455,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>C004065232</t>
+          <t>C001086594</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C004065232 - AGUADO LOPEZ CHAI TIODOLINDA</t>
+          <t>C001086594 - RAMOS CAHUANA SONIA ISABEL</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>S17842164</t>
+          <t>S17840713</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1530,14 +1530,14 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97978</v>
+        <v>4780</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>C001158905</t>
+          <t>C000957808</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>C001158905 - DIAZ PEREZ ELIZABETH</t>
+          <t>C000957808 - NAPANGA PEREZ BALBINA ISIDORA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>S17851802</t>
+          <t>S17842189</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1885,7 +1885,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>23595</v>
+        <v>110940</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>C001379080</t>
+          <t>C004049669</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>C001379080 - MORAN DE GONZALES ROSA MARIA</t>
+          <t>C004049669 - HERRERA AGUIRRE CINDY</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>S17772780</t>
+          <t>S17770983</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +2001,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3634</v>
+        <v>23595</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2035,12 +2035,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>C000962609</t>
+          <t>C001379080</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>C000962609 - RODRIGUEZ GUILLEN DAYSI</t>
+          <t>C001379080 - MORAN DE GONZALES ROSA MARIA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2060,11 +2060,11 @@
         <v>46235</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>S17835652</t>
+          <t>S17772780</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2100,7 +2100,7 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2110,14 +2110,14 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110940</v>
+        <v>3634</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>C004049669</t>
+          <t>C000962609</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>C004049669 - HERRERA AGUIRRE CINDY</t>
+          <t>C000962609 - RODRIGUEZ GUILLEN DAYSI</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2176,11 +2176,11 @@
         <v>46235</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>S17770983</t>
+          <t>S17835652</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2216,24 +2216,24 @@
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110358</v>
+        <v>18256</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2267,12 +2267,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>C000959895</t>
+          <t>C001307050</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>C000959895 - SARAVIA SARAVIA JOSE MERCEDES</t>
+          <t>C001307050 - QUISPE NORMA BERNARDINA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2292,11 +2292,11 @@
         <v>46235</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>S17811291</t>
+          <t>S17838324</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2332,24 +2332,24 @@
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96882</v>
+        <v>30280</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2383,12 +2383,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>C000956334</t>
+          <t>C001556504</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>C000956334 - FELIX DE ROJAS MARIA AUGUSTA</t>
+          <t>C001556504 - SALVATIERRA MACHUCA KARIN ELIANA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2408,11 +2408,11 @@
         <v>46235</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>S17779202</t>
+          <t>S17855219</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>No cuenta con presupuesto disponible en ese momento.</t>
+          <t>Otros motivos</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2448,12 +2448,12 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,7 +2465,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89142</v>
+        <v>60111</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2499,12 +2499,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>C004001810</t>
+          <t>C001723032</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>C004001810 - CAYCHO HUAMAN OLGA LIDIA</t>
+          <t>C001723032 - QUISPE PALOMINO EDDIE MERINIYES</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>S17752632</t>
+          <t>S17748142</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2574,14 +2574,14 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>30280</v>
+        <v>110358</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2615,12 +2615,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>C001556504</t>
+          <t>C000959895</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>C001556504 - SALVATIERRA MACHUCA KARIN ELIANA</t>
+          <t>C000959895 - SARAVIA SARAVIA JOSE MERCEDES</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2640,11 +2640,11 @@
         <v>46235</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>S17855219</t>
+          <t>S17811291</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Otros motivos</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2680,7 +2680,7 @@
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2690,14 +2690,14 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18256</v>
+        <v>96882</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2731,12 +2731,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>C001307050</t>
+          <t>C000956334</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>C001307050 - QUISPE NORMA BERNARDINA</t>
+          <t>C000956334 - FELIX DE ROJAS MARIA AUGUSTA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2756,11 +2756,11 @@
         <v>46235</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>S17838324</t>
+          <t>S17779202</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>No cuenta con presupuesto disponible en ese momento.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2796,7 +2796,7 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2813,7 +2813,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>60111</v>
+        <v>89142</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2847,12 +2847,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>C001723032</t>
+          <t>C004001810</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>C001723032 - QUISPE PALOMINO EDDIE MERINIYES</t>
+          <t>C004001810 - CAYCHO HUAMAN OLGA LIDIA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>S17748142</t>
+          <t>S17752632</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2922,14 +2922,14 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>63570</v>
+        <v>74210</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2963,12 +2963,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>C004094381</t>
+          <t>C004038222</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>C004094381 - TORRES RIVAS DAYANA KAREN</t>
+          <t>C004038222 - VILCAPUMA LAURA RUBY EDELYN</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2988,11 +2988,11 @@
         <v>46235</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>S17789850</t>
+          <t>S17847009</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3033,19 +3033,19 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Más capacitación</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>64633</v>
+        <v>73867</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3079,12 +3079,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>C004011479</t>
+          <t>C001728535</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>C004011479 - MAGUINA LOPEZ SHIRLEY DESSIREDT</t>
+          <t>C001728535 - AURIS CHAVEZ DE CASTILLON ALICIA MARTINA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3104,11 +3104,11 @@
         <v>46235</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>S17714461</t>
+          <t>S17735036</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3144,7 +3144,7 @@
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3161,7 +3161,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>53994</v>
+        <v>66885</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3195,12 +3195,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>C001551841</t>
+          <t>C004172212</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>C001551841 - TASAYCO MAGALLANES YEISY MEDALIT</t>
+          <t>C004172212 - MORALES ROMERO SILVIA ROSARIO</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>S17721110</t>
+          <t>S17716707</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3277,7 +3277,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>50036</v>
+        <v>73449</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3311,12 +3311,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>C001737256</t>
+          <t>C004169879</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>C001737256 - RAMOS ROMERO MARILUZ LILIANA</t>
+          <t>C004169879 - CHAVEZ CAHUANA LILI ZUNILDA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3336,11 +3336,11 @@
         <v>46235</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>S17740324</t>
+          <t>S17847087</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3376,7 +3376,7 @@
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3393,7 +3393,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>22016</v>
+        <v>102849</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3427,12 +3427,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>C001522451</t>
+          <t>C001517282</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>C001522451 - CARCAMO DE ROJAS DACIANA</t>
+          <t>C001517282 - CLAROS FELIX JESSICA DEL ROSARIO</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>S17724127</t>
+          <t>S17718140</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3509,7 +3509,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>24264</v>
+        <v>64633</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3543,12 +3543,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>C001498029</t>
+          <t>C004011479</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>C001498029 - CASTILLON HERRERA KLEYBER YONZON</t>
+          <t>C004011479 - MAGUINA LOPEZ SHIRLEY DESSIREDT</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3568,11 +3568,11 @@
         <v>46235</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>46244</v>
+        <v>46242</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>S17744377</t>
+          <t>S17714461</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3625,7 +3625,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>10817</v>
+        <v>63570</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>C000957880</t>
+          <t>C004094381</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>C000957880 - CHAVEZ BAUTISTA DE MANSILLA MARISA OFELI</t>
+          <t>C004094381 - TORRES RIVAS DAYANA KAREN</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3684,11 +3684,11 @@
         <v>46235</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>46242</v>
+        <v>46245</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>S17719211</t>
+          <t>S17789850</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3724,24 +3724,24 @@
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Más capacitación</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>16647</v>
+        <v>53994</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3775,12 +3775,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>C001365658</t>
+          <t>C001551841</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>C001365658 - PAUCAR CRISOSTOMO ZENAIDA SEREGIA</t>
+          <t>C001551841 - TASAYCO MAGALLANES YEISY MEDALIT</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3800,11 +3800,11 @@
         <v>46235</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>46244</v>
+        <v>46242</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>S17735256</t>
+          <t>S17721110</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3840,7 +3840,7 @@
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>Nada dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -3857,7 +3857,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>74210</v>
+        <v>50036</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>C004038222</t>
+          <t>C001737256</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>C004038222 - VILCAPUMA LAURA RUBY EDELYN</t>
+          <t>C001737256 - RAMOS ROMERO MARILUZ LILIANA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3916,11 +3916,11 @@
         <v>46235</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>46247</v>
+        <v>46244</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>S17847009</t>
+          <t>S17740324</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3973,7 +3973,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>66885</v>
+        <v>22016</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -4007,12 +4007,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>C004172212</t>
+          <t>C001522451</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>C004172212 - MORALES ROMERO SILVIA ROSARIO</t>
+          <t>C001522451 - CARCAMO DE ROJAS DACIANA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>S17716707</t>
+          <t>S17724127</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4072,12 +4072,12 @@
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4089,7 +4089,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>73449</v>
+        <v>24264</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4123,12 +4123,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>C004169879</t>
+          <t>C001498029</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>C004169879 - CHAVEZ CAHUANA LILI ZUNILDA</t>
+          <t>C001498029 - CASTILLON HERRERA KLEYBER YONZON</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4148,11 +4148,11 @@
         <v>46235</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>46247</v>
+        <v>46244</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>S17847087</t>
+          <t>S17744377</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4188,12 +4188,12 @@
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4205,7 +4205,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>73867</v>
+        <v>10817</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4239,12 +4239,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>C001728535</t>
+          <t>C000957880</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>C001728535 - AURIS CHAVEZ DE CASTILLON ALICIA MARTINA</t>
+          <t>C000957880 - CHAVEZ BAUTISTA DE MANSILLA MARISA OFELI</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4264,11 +4264,11 @@
         <v>46235</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>46244</v>
+        <v>46242</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>S17735036</t>
+          <t>S17719211</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4314,14 +4314,14 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>102849</v>
+        <v>16647</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4355,12 +4355,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>C001517282</t>
+          <t>C001365658</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>C001517282 - CLAROS FELIX JESSICA DEL ROSARIO</t>
+          <t>C001365658 - PAUCAR CRISOSTOMO ZENAIDA SEREGIA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4380,11 +4380,11 @@
         <v>46235</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>S17718140</t>
+          <t>S17735256</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4420,12 +4420,12 @@
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Nada dispuesto</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4437,7 +4437,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>96000</v>
+        <v>8214</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4471,12 +4471,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>C004179159</t>
+          <t>C000957338</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>C004179159 - SILVA VILCHERREZ CARITO ELIZABETH</t>
+          <t>C000957338 - ATUNCAR CASTA EDA ROSA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4496,11 +4496,11 @@
         <v>46235</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>S17691427</t>
+          <t>S17824912</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4536,24 +4536,24 @@
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>72745</v>
+        <v>4664</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>C004030084</t>
+          <t>C000961008</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>C004030084 - ATUNCAR FUENTES ELIZABETH PAOLA</t>
+          <t>C000961008 - ALMEYDA MATIAS HUGO</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4612,11 +4612,11 @@
         <v>46235</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>S17683091</t>
+          <t>S17712337</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4657,19 +4657,19 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>69801</v>
+        <v>24850</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>C004039883</t>
+          <t>C001490980</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>C004039883 - OCHOA PACHAS DE MENDOZA SOLEDAD</t>
+          <t>C001490980 - ROJAS ATUNCAR VICTOR JAVIER</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>S17723620</t>
+          <t>S17718443</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4763,7 +4763,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr">
@@ -4778,14 +4782,14 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>91431</v>
+        <v>24172</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4819,12 +4823,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>C004039877</t>
+          <t>C001403893</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>C004039877 - NAVARRO MARCELO ANITA</t>
+          <t>C001403893 - SALCEDO FALCONI IDA PAULINA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4844,11 +4848,11 @@
         <v>46235</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>46242</v>
+        <v>46246</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>S17713780</t>
+          <t>S17825974</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4871,7 +4875,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4901,7 +4905,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>8214</v>
+        <v>27918</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4935,12 +4939,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>C000957338</t>
+          <t>C001370197</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>C000957338 - ATUNCAR CASTA EDA ROSA</t>
+          <t>C001370197 - DE LA CRUZ DE GENTILLE DORIS GUILLERMINA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4960,11 +4964,11 @@
         <v>46235</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>S17824912</t>
+          <t>S17725296</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4987,7 +4991,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5000,7 +5004,7 @@
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -5017,7 +5021,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4664</v>
+        <v>45437</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -5051,12 +5055,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>C000961008</t>
+          <t>C001555062</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>C000961008 - ALMEYDA MATIAS HUGO</t>
+          <t>C001555062 - CHAVEZ PRADA DE CANELO NELLY VICTORIA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5080,7 +5084,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>S17712337</t>
+          <t>S17720347</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5103,7 +5107,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5116,7 +5120,7 @@
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -5126,14 +5130,14 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>27918</v>
+        <v>57902</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -5167,12 +5171,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>C001370197</t>
+          <t>C004030082</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>C001370197 - DE LA CRUZ DE GENTILLE DORIS GUILLERMINA</t>
+          <t>C004030082 - YATACO MUNAYCO YSABEL</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5192,11 +5196,11 @@
         <v>46235</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>46242</v>
+        <v>46246</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>S17725296</t>
+          <t>S17813826</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5219,7 +5223,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5237,7 +5241,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5249,7 +5253,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>24172</v>
+        <v>60354</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5283,12 +5287,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>C001403893</t>
+          <t>C004044079</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>C001403893 - SALCEDO FALCONI IDA PAULINA</t>
+          <t>C004044079 - VALLADARES ESPINOZA GLADYS MARILU</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5308,11 +5312,11 @@
         <v>46235</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>S17825974</t>
+          <t>S17713473</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5365,7 +5369,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>24850</v>
+        <v>96000</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -5399,12 +5403,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>C001490980</t>
+          <t>C004179159</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>C001490980 - ROJAS ATUNCAR VICTOR JAVIER</t>
+          <t>C004179159 - SILVA VILCHERREZ CARITO ELIZABETH</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5424,11 +5428,11 @@
         <v>46235</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>S17718443</t>
+          <t>S17691427</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5451,7 +5455,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5459,21 +5463,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5485,7 +5485,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>45437</v>
+        <v>72745</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>C001555062</t>
+          <t>C004030084</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>C001555062 - CHAVEZ PRADA DE CANELO NELLY VICTORIA</t>
+          <t>C004030084 - ATUNCAR FUENTES ELIZABETH PAOLA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5544,11 +5544,11 @@
         <v>46235</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>S17720347</t>
+          <t>S17683091</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5584,12 +5584,12 @@
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5601,7 +5601,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>57902</v>
+        <v>69801</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -5635,12 +5635,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>C004030082</t>
+          <t>C004039883</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>C004030082 - YATACO MUNAYCO YSABEL</t>
+          <t>C004039883 - OCHOA PACHAS DE MENDOZA SOLEDAD</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5660,11 +5660,11 @@
         <v>46235</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>S17813826</t>
+          <t>S17723620</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5717,7 +5717,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>60354</v>
+        <v>91431</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>C004044079</t>
+          <t>C004039877</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>C004044079 - VALLADARES ESPINOZA GLADYS MARILU</t>
+          <t>C004039877 - NAVARRO MARCELO ANITA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>S17713473</t>
+          <t>S17713780</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5833,7 +5833,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>63540</v>
+        <v>84034</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>C004014163</t>
+          <t>C004215343</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>C004014163 - PACHAS POLO NOEMI</t>
+          <t>C004215343 - DE LA CRUZ DE LA CRUZ DE LUYO MELVI</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>S17562428</t>
+          <t>S17560630</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5937,19 +5937,19 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>Agregar productos al carrito</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>40020</v>
+        <v>93963</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>C001450755</t>
+          <t>C004188867</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>C001450755 - RONCEROS ÑAÑEZ GIOVANA ELIZABETH</t>
+          <t>C004188867 - ALMEYDA GUTIERREZ LUCILA MARGARITA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6008,11 +6008,11 @@
         <v>46235</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>46245</v>
+        <v>46238</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>S17781612</t>
+          <t>S17589769</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6065,7 +6065,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>36177</v>
+        <v>100219</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>C001646860</t>
+          <t>C000960371</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>C001646860 - MARTINEZ VALENCIA JULLIANA DEL CARMEN</t>
+          <t>C000960371 - HUASASQUICHE ASTORAYME VILMA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6124,11 +6124,11 @@
         <v>46235</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>46240</v>
+        <v>46237</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>S17648980</t>
+          <t>S17575698</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6164,12 +6164,12 @@
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6181,7 +6181,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>26195</v>
+        <v>104797</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -6215,12 +6215,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>C001526666</t>
+          <t>C001723581</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>C001526666 - CANALES AYLLON YESSICA KELLY</t>
+          <t>C001723581 - PAUCAR CHOQUE FLORINDA GLADYS</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>S17557365</t>
+          <t>S17554099</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6280,7 +6280,7 @@
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
@@ -6297,7 +6297,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>17691</v>
+        <v>63540</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>C001319626</t>
+          <t>C004014163</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>C001319626 - TUPAC VILCAPUMA MARITZA EDITH</t>
+          <t>C004014163 - PACHAS POLO NOEMI</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6356,11 +6356,11 @@
         <v>46235</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>S17583734</t>
+          <t>S17562428</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -6396,12 +6396,12 @@
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Agregar productos al carrito</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6413,7 +6413,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>15966</v>
+        <v>36177</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -6447,12 +6447,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>C000961456</t>
+          <t>C001646860</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>C000961456 - SUAREZ DE WONG VERONICA ISABEL</t>
+          <t>C001646860 - MARTINEZ VALENCIA JULLIANA DEL CARMEN</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6472,11 +6472,11 @@
         <v>46235</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>S17598622</t>
+          <t>S17648980</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6512,12 +6512,12 @@
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6529,7 +6529,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>11060</v>
+        <v>40020</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -6563,12 +6563,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>C000957551</t>
+          <t>C001450755</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>C000957551 - RAMIREZ DE MATTA ESPERANZA</t>
+          <t>C001450755 - RONCEROS ÑAÑEZ GIOVANA ELIZABETH</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6588,11 +6588,11 @@
         <v>46235</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>S17571098</t>
+          <t>S17781612</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6645,7 +6645,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>84034</v>
+        <v>26195</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>C004215343</t>
+          <t>C001526666</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>C004215343 - DE LA CRUZ DE LA CRUZ DE LUYO MELVI</t>
+          <t>C001526666 - CANALES AYLLON YESSICA KELLY</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>S17560630</t>
+          <t>S17557365</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6744,7 +6744,7 @@
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
@@ -6754,14 +6754,14 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>93963</v>
+        <v>17691</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -6795,12 +6795,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>C004188867</t>
+          <t>C001319626</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>C004188867 - ALMEYDA GUTIERREZ LUCILA MARGARITA</t>
+          <t>C001319626 - TUPAC VILCAPUMA MARITZA EDITH</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>S17589769</t>
+          <t>S17583734</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6860,7 +6860,7 @@
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
@@ -6877,7 +6877,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>100219</v>
+        <v>15966</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>C000960371</t>
+          <t>C000961456</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>C000960371 - HUASASQUICHE ASTORAYME VILMA</t>
+          <t>C000961456 - SUAREZ DE WONG VERONICA ISABEL</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6936,11 +6936,11 @@
         <v>46235</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>S17575698</t>
+          <t>S17598622</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6993,7 +6993,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>104797</v>
+        <v>11060</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -7027,12 +7027,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>C001723581</t>
+          <t>C000957551</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>C001723581 - PAUCAR CHOQUE FLORINDA GLADYS</t>
+          <t>C000957551 - RAMIREZ DE MATTA ESPERANZA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>S17554099</t>
+          <t>S17571098</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7109,7 +7109,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>109640</v>
+        <v>15944</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -7143,12 +7143,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>C004187618</t>
+          <t>C001391394</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>C004187618 - QUISPE DE PACHAS ANA MARIA</t>
+          <t>C001391394 - FARFAN CHIRA MARILU GIOVANA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7168,11 +7168,11 @@
         <v>46235</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>S17543307</t>
+          <t>S17686667</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -7208,24 +7208,24 @@
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>102850</v>
+        <v>14634</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -7259,12 +7259,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>C001731574</t>
+          <t>C001198608</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>C001731574 - GARAY RAMOS GIANCARLO</t>
+          <t>C001198608 - SUAREZ VALLADARES JAQUELIN ROXANA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7284,11 +7284,11 @@
         <v>46235</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>S17535615</t>
+          <t>S17594397</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -7324,7 +7324,7 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
@@ -7341,7 +7341,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>80483</v>
+        <v>26196</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>C004178891</t>
+          <t>C001461205</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>C004178891 - MOLINA FUENTES DE MORE ELIZABETH</t>
+          <t>C001461205 - SALCEDO SERVELEON AIDA TEOFILA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7400,11 +7400,11 @@
         <v>46235</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>46239</v>
+        <v>46235</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>S17642447</t>
+          <t>S17541752</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -7440,24 +7440,24 @@
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>92222</v>
+        <v>27467</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>C004016311</t>
+          <t>C001476354</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>C004016311 - HUACCAMAYTA ALMEYDA ELIZABETH CELESTE</t>
+          <t>C001476354 - SANTIAGO CANCHARI TEODOMIRA ZONIA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7516,11 +7516,11 @@
         <v>46235</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>46241</v>
+        <v>46235</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>S17697424</t>
+          <t>S17532697</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7551,29 +7551,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr"/>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>86234</v>
+        <v>24079</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -7607,12 +7611,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>C001506187</t>
+          <t>C001423708</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>C001506187 - CAYCHO FLORES DE GUTIERREZ LUCILA DORA</t>
+          <t>C001423708 - MUNARES LOZA OLGA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7636,7 +7640,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>S17594925</t>
+          <t>S17587830</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7659,7 +7663,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7689,7 +7693,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>74907</v>
+        <v>17802</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -7723,12 +7727,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>C004178624</t>
+          <t>C001373321</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>C004178624 - ROJAS OSCO SARITA</t>
+          <t>C001373321 - HUAMAN FELIX CARMEN BARBARITA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7748,11 +7752,11 @@
         <v>46235</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>S17604548</t>
+          <t>S17580623</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7775,7 +7779,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>No cuenta con presupuesto disponible en ese momento.</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7805,7 +7809,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>79358</v>
+        <v>57783</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -7839,12 +7843,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>C004243882</t>
+          <t>C004042194</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>C004243882 - ELIAS MUNAYCO MARIA GREGORIA</t>
+          <t>C004042194 - MOREYRA TAYPE BEATRIZ</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7864,11 +7868,11 @@
         <v>46235</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>46238</v>
+        <v>46235</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>S17583157</t>
+          <t>S17536888</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7891,7 +7895,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7904,7 +7908,7 @@
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
@@ -7921,7 +7925,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>69802</v>
+        <v>66652</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -7955,12 +7959,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>C004060593</t>
+          <t>C004212960</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>C004060593 - VALENTIN HUAMAN ROBERTO MARCELINO</t>
+          <t>C004212960 - CHANCA DE LA MATA SABINA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7980,11 +7984,11 @@
         <v>46235</v>
       </c>
       <c r="N65" s="3" t="n">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>S17677074</t>
+          <t>S17599198</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8007,7 +8011,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -8020,12 +8024,12 @@
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8037,7 +8041,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>73586</v>
+        <v>66558</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -8071,12 +8075,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>C004175861</t>
+          <t>C004180907</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>C004175861 - HERNANDEZ COELLO CARLOS JOHAO</t>
+          <t>C004180907 - VALLE CUETO PIERINA GEORGINA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8096,11 +8100,11 @@
         <v>46235</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>46244</v>
+        <v>46238</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>S17738930</t>
+          <t>S17606231</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8136,7 +8140,7 @@
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
@@ -8146,14 +8150,14 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>15944</v>
+        <v>61146</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -8187,12 +8191,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>C001391394</t>
+          <t>C004028239</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>C001391394 - FARFAN CHIRA MARILU GIOVANA</t>
+          <t>C004028239 - DE LOS RIOS SALVATIERRA DIANA LIZBETH</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8212,11 +8216,11 @@
         <v>46235</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>46241</v>
+        <v>46235</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>S17686667</t>
+          <t>S17536267</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8262,14 +8266,14 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>14634</v>
+        <v>109640</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -8303,12 +8307,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>C001198608</t>
+          <t>C004187618</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>C001198608 - SUAREZ VALLADARES JAQUELIN ROXANA</t>
+          <t>C004187618 - QUISPE DE PACHAS ANA MARIA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8328,11 +8332,11 @@
         <v>46235</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>46238</v>
+        <v>46235</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>S17594397</t>
+          <t>S17543307</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8355,7 +8359,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -8373,7 +8377,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8385,7 +8389,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>26196</v>
+        <v>102850</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -8419,12 +8423,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>C001461205</t>
+          <t>C001731574</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>C001461205 - SALCEDO SERVELEON AIDA TEOFILA</t>
+          <t>C001731574 - GARAY RAMOS GIANCARLO</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8448,7 +8452,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>S17541752</t>
+          <t>S17535615</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8489,19 +8493,19 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>27467</v>
+        <v>80483</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -8535,12 +8539,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>C001476354</t>
+          <t>C004178891</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>C001476354 - SANTIAGO CANCHARI TEODOMIRA ZONIA</t>
+          <t>C004178891 - MOLINA FUENTES DE MORE ELIZABETH</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8560,11 +8564,11 @@
         <v>46235</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>46235</v>
+        <v>46239</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>S17532697</t>
+          <t>S17642447</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8587,7 +8591,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8595,21 +8599,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8621,7 +8621,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>24079</v>
+        <v>92222</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -8655,12 +8655,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>C001423708</t>
+          <t>C004016311</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>C001423708 - MUNARES LOZA OLGA</t>
+          <t>C004016311 - HUACCAMAYTA ALMEYDA ELIZABETH CELESTE</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8680,11 +8680,11 @@
         <v>46235</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>S17587830</t>
+          <t>S17697424</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8720,24 +8720,24 @@
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>17802</v>
+        <v>86234</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -8771,12 +8771,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>C001373321</t>
+          <t>C001506187</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>C001373321 - HUAMAN FELIX CARMEN BARBARITA</t>
+          <t>C001506187 - CAYCHO FLORES DE GUTIERREZ LUCILA DORA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8796,11 +8796,11 @@
         <v>46235</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>S17580623</t>
+          <t>S17594925</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>No cuenta con presupuesto disponible en ese momento.</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8836,12 +8836,12 @@
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8853,7 +8853,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>57783</v>
+        <v>74907</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -8887,12 +8887,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>C004042194</t>
+          <t>C004178624</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>C004042194 - MOREYRA TAYPE BEATRIZ</t>
+          <t>C004178624 - ROJAS OSCO SARITA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8912,11 +8912,11 @@
         <v>46235</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>S17536888</t>
+          <t>S17604548</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8952,12 +8952,12 @@
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8969,7 +8969,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>66652</v>
+        <v>79358</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -9003,12 +9003,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>C004212960</t>
+          <t>C004243882</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>C004212960 - CHANCA DE LA MATA SABINA</t>
+          <t>C004243882 - ELIAS MUNAYCO MARIA GREGORIA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>S17599198</t>
+          <t>S17583157</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -9068,12 +9068,12 @@
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9085,7 +9085,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>66558</v>
+        <v>69802</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -9119,12 +9119,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>C004180907</t>
+          <t>C004060593</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>C004180907 - VALLE CUETO PIERINA GEORGINA</t>
+          <t>C004060593 - VALENTIN HUAMAN ROBERTO MARCELINO</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9144,11 +9144,11 @@
         <v>46235</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>S17606231</t>
+          <t>S17677074</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -9189,19 +9189,19 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>61146</v>
+        <v>73586</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -9235,12 +9235,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>C004028239</t>
+          <t>C004175861</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>C004028239 - DE LOS RIOS SALVATIERRA DIANA LIZBETH</t>
+          <t>C004175861 - HERNANDEZ COELLO CARLOS JOHAO</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9260,11 +9260,11 @@
         <v>46235</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>46235</v>
+        <v>46244</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>S17536267</t>
+          <t>S17738930</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9300,7 +9300,7 @@
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
